--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:40</t>
+    <t xml:space="preserve">2026-08-02 20:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:07</t>
+    <t xml:space="preserve">2026-08-16 10:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:14</t>
+    <t xml:space="preserve">2026-08-19 14:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:42</t>
+    <t xml:space="preserve">2026-08-28 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2024_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:40</t>
+    <t xml:space="preserve">2026-09-06 17:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
